--- a/ig/main/ValueSet-vs-tre-r373-type-personne-morale-all.xlsx
+++ b/ig/main/ValueSet-vs-tre-r373-type-personne-morale-all.xlsx
@@ -8,12 +8,14 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -106,6 +108,45 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r373-type-personne-morale</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r373-type-personne-morale|20260505120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Personne morale d'exercice (Exercice)</t>
   </si>
 </sst>
 </file>
@@ -397,4 +438,92 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/main/ValueSet-vs-tre-r373-type-personne-morale-all.xlsx
+++ b/ig/main/ValueSet-vs-tre-r373-type-personne-morale-all.xlsx
@@ -8,14 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
-    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Property</t>
   </si>
@@ -108,45 +106,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r373-type-personne-morale</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>used-codesystem</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r373-type-personne-morale|20260505120000</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Personne morale d'exercice (Exercice)</t>
   </si>
 </sst>
 </file>
@@ -438,92 +397,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>